--- a/docs/legal/review-2026-06-16/rj-ronald-j-antonelli/word/12-rj-cap-table-update.xlsx
+++ b/docs/legal/review-2026-06-16/rj-ronald-j-antonelli/word/12-rj-cap-table-update.xlsx
@@ -493,7 +493,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Charles Petrini Poli</t>
+          <t>Charles Petrini-Poli</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
